--- a/data/trans_orig/P32D_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32D_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses ha tomado 6/5 (Hombre/Mujer) o más bebidas estándar en una misma ocasión en 2023</t>
+          <t>Población según si en los últimos 12 meses ha tomado 6/5 (Hombre/Mujer) o más bebidas estándar en una misma ocasión en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86837</t>
+          <t>87027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117097</t>
+          <t>115620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69188</t>
+          <t>68936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80708</t>
+          <t>81037</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160253</t>
+          <t>162763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>194397</t>
+          <t>194072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43655</t>
+          <t>45567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72692</t>
+          <t>72164</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17316</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53918</t>
+          <t>54021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83848</t>
+          <t>83331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24195</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24761</t>
+          <t>25070</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11778</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>11583</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>341</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59863</t>
+          <t>58261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100825</t>
+          <t>100564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53256</t>
+          <t>52052</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73492</t>
+          <t>74996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117677</t>
+          <t>121204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168110</t>
+          <t>167339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,91%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>105348</t>
+          <t>105538</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>149490</t>
+          <t>147737</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29413</t>
+          <t>29324</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49276</t>
+          <t>49241</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>141360</t>
+          <t>144581</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>191864</t>
+          <t>189514</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31413</t>
+          <t>31273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>20213</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22008</t>
+          <t>21772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45794</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32366</t>
+          <t>34079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34482</t>
+          <t>36360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13441</t>
+          <t>13698</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16016</t>
+          <t>17022</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13772</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17299</t>
+          <t>17773</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34719</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>27921</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45414</t>
+          <t>45534</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>48737</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>73972</t>
+          <t>75813</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73251</t>
+          <t>72243</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99576</t>
+          <t>99308</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23791</t>
+          <t>24055</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>40193</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>99780</t>
+          <t>99898</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>130264</t>
+          <t>131048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35085</t>
+          <t>34370</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59048</t>
+          <t>58605</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29697</t>
+          <t>28609</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>53240</t>
+          <t>53063</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>81550</t>
+          <t>81157</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>20316</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>22239</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15548</t>
+          <t>15560</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>629</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17785</t>
+          <t>17976</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>53809</t>
+          <t>58086</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>35742</t>
+          <t>36678</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>54324</t>
+          <t>56329</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>59604</t>
+          <t>60934</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>99110</t>
+          <t>96593</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -4245,12 +4245,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>65077</t>
+          <t>67281</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>99916</t>
+          <t>100294</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>37748</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>56441</t>
+          <t>56603</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4315,12 +4315,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>110669</t>
+          <t>112635</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>149880</t>
+          <t>150020</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,95%</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>27512</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>57488</t>
+          <t>56717</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>28337</t>
+          <t>29885</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>43490</t>
+          <t>42841</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>76521</t>
+          <t>75732</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4471,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>23278</t>
+          <t>23341</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4584,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13654</t>
+          <t>14335</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>20817</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4697,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>873</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>20391</t>
+          <t>19012</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>830</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>21442</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -5266,12 +5266,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -5379,12 +5379,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>21403</t>
+          <t>21387</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5394,12 +5394,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5449,12 +5449,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>15355</t>
+          <t>14707</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>26008</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -5492,12 +5492,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -5605,12 +5605,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>469</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>272</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>874</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>171</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -5831,12 +5831,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -5944,12 +5944,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6057,12 +6057,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6142,12 +6142,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -6400,12 +6400,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>27780</t>
+          <t>27465</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>40650</t>
+          <t>40519</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>42266</t>
+          <t>42190</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>63560</t>
+          <t>63339</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6485,12 +6485,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -6513,12 +6513,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>57693</t>
+          <t>57379</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>81506</t>
+          <t>81009</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>27895</t>
+          <t>28142</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>42759</t>
+          <t>44381</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>92184</t>
+          <t>91714</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>121271</t>
+          <t>119757</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -6626,12 +6626,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>27810</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>47814</t>
+          <t>48461</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>25790</t>
+          <t>25725</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>42152</t>
+          <t>43097</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>67755</t>
+          <t>68187</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>18316</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6789,12 +6789,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>23572</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>19723</t>
+          <t>19951</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -7078,12 +7078,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -7191,12 +7191,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7304,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>10134</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>54962</t>
+          <t>56296</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>88066</t>
+          <t>90164</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>162942</t>
+          <t>167123</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>364233</t>
+          <t>364731</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>209992</t>
+          <t>212015</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>551986</t>
+          <t>549813</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,29%</t>
         </is>
       </c>
     </row>
@@ -7647,12 +7647,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>69968</t>
+          <t>69816</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>103602</t>
+          <t>104491</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>95891</t>
+          <t>97114</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>58865</t>
+          <t>53163</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>193172</t>
+          <t>193283</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>56796</t>
+          <t>56474</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>95973</t>
+          <t>95666</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>9771</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>86709</t>
+          <t>84563</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>47970</t>
+          <t>50389</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>167056</t>
+          <t>166209</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -7873,12 +7873,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>24729</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>68270</t>
+          <t>67131</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7888,12 +7888,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>30067</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>20795</t>
+          <t>21896</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>85365</t>
+          <t>85866</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>25857</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8001,12 +8001,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>277</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>15949</t>
+          <t>16495</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>36398</t>
+          <t>36117</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -8099,12 +8099,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>879</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>22974</t>
+          <t>21888</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>32748</t>
+          <t>33905</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -8212,12 +8212,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>161</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8297,12 +8297,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>855</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8375,12 +8375,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>8859</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -8438,12 +8438,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8665</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8453,12 +8453,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -8668,12 +8668,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>9829</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>12552</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>30082</t>
+          <t>32013</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>95121</t>
+          <t>92617</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>126620</t>
+          <t>124472</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>43091</t>
+          <t>43002</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>60514</t>
+          <t>60261</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8831,12 +8831,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>141173</t>
+          <t>143507</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>178878</t>
+          <t>180765</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8866,12 +8866,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -8894,12 +8894,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>74781</t>
+          <t>72661</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>103718</t>
+          <t>103116</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8909,12 +8909,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>31635</t>
+          <t>31936</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8944,12 +8944,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>95887</t>
+          <t>95022</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>130318</t>
+          <t>129203</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8979,12 +8979,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -9007,12 +9007,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>30625</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9042,12 +9042,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9057,12 +9057,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9077,12 +9077,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>33225</t>
+          <t>34618</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>11044</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>30258</t>
+          <t>31092</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>9432</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9170,12 +9170,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9190,12 +9190,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>34238</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -9233,12 +9233,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>25272</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -9268,12 +9268,12 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9283,12 +9283,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9303,12 +9303,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>15223</t>
+          <t>15052</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>33113</t>
+          <t>33021</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -9572,12 +9572,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8196</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>309402</t>
+          <t>307992</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>388854</t>
+          <t>387547</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9837,12 +9837,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>419980</t>
+          <t>422717</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>758170</t>
+          <t>751416</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9852,12 +9852,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>729855</t>
+          <t>733316</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>1312763</t>
+          <t>1398915</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>591606</t>
+          <t>592431</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>677629</t>
+          <t>681719</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9930,12 +9930,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>146035</t>
+          <t>148682</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>336124</t>
+          <t>336556</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9965,12 +9965,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9985,12 +9985,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>687339</t>
+          <t>657914</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>993364</t>
+          <t>997132</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -10000,12 +10000,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -10028,12 +10028,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>293663</t>
+          <t>293479</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>366923</t>
+          <t>366401</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10043,12 +10043,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>68093</t>
+          <t>75521</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>170117</t>
+          <t>168930</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>337885</t>
+          <t>324634</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>515023</t>
+          <t>508338</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -10141,12 +10141,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>94259</t>
+          <t>93262</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>153133</t>
+          <t>153409</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10156,12 +10156,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>42022</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>110020</t>
+          <t>108593</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>180423</t>
+          <t>180258</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>45328</t>
+          <t>46504</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>82586</t>
+          <t>81747</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10269,12 +10269,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>40107</t>
+          <t>38885</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>63503</t>
+          <t>63380</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>111173</t>
+          <t>109674</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -10367,12 +10367,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>37933</t>
+          <t>37982</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>68484</t>
+          <t>68339</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10382,12 +10382,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10402,12 +10402,12 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>53246</t>
+          <t>53457</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>95882</t>
+          <t>93757</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -10480,12 +10480,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10515,12 +10515,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -10593,12 +10593,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10608,12 +10608,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10628,12 +10628,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -10706,12 +10706,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -10721,12 +10721,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>34160</t>
+          <t>33648</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32D_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32D_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>101983</t>
+          <t>98399</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87027</t>
+          <t>86382</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115620</t>
+          <t>110621</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>76059</t>
+          <t>79483</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68936</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81037</t>
+          <t>84910</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>178042</t>
+          <t>177881</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>162763</t>
+          <t>162251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>194072</t>
+          <t>191487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,68%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57313</t>
+          <t>54114</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45567</t>
+          <t>42406</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72164</t>
+          <t>65657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>19085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>68112</t>
+          <t>67049</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54021</t>
+          <t>54976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83331</t>
+          <t>82533</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>19886</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7523</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25070</t>
+          <t>20228</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>773</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9449</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -1742,17 +1742,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>78795</t>
+          <t>75995</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58261</t>
+          <t>59489</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100564</t>
+          <t>98569</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>63019</t>
+          <t>67680</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52052</t>
+          <t>56211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74996</t>
+          <t>77914</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>141813</t>
+          <t>143675</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121204</t>
+          <t>119533</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167339</t>
+          <t>166864</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>43,6%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>128448</t>
+          <t>132335</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>105538</t>
+          <t>111147</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>147737</t>
+          <t>151589</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38977</t>
+          <t>39709</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>30330</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49241</t>
+          <t>50464</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>167425</t>
+          <t>172044</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>144581</t>
+          <t>151295</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>189514</t>
+          <t>199137</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>24540</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31273</t>
+          <t>36941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>20830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>36738</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>23171</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45691</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>16993</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34079</t>
+          <t>31270</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19040</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36360</t>
+          <t>34632</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1508</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13698</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -2424,32 +2424,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12569</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>704</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12507</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>255636</t>
+          <t>259856</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255636</t>
+          <t>259856</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>255636</t>
+          <t>259856</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>372606</t>
+          <t>382739</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>372606</t>
+          <t>382739</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>372606</t>
+          <t>382739</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24992</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17773</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35704</t>
+          <t>33600</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36219</t>
+          <t>34243</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>27921</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45534</t>
+          <t>41975</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>61211</t>
+          <t>58772</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>48737</t>
+          <t>46275</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>75813</t>
+          <t>71122</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -3106,32 +3106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>85371</t>
+          <t>87045</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72243</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99308</t>
+          <t>100353</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3141,32 +3141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>30773</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24055</t>
+          <t>23621</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40193</t>
+          <t>39769</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3176,32 +3176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>116144</t>
+          <t>118559</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>99898</t>
+          <t>103313</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>131048</t>
+          <t>134231</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>46113</t>
+          <t>46326</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34370</t>
+          <t>34421</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58605</t>
+          <t>58372</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3254,32 +3254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>20201</t>
+          <t>20360</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>13997</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28609</t>
+          <t>28368</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,32 +3289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>66313</t>
+          <t>66686</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>53063</t>
+          <t>54083</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>81157</t>
+          <t>80882</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -3332,32 +3332,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20316</t>
+          <t>18123</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3377,12 +3377,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3402,32 +3402,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>13051</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22239</t>
+          <t>21511</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -3445,32 +3445,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>944</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>15797</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -3558,102 +3558,102 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>4805</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>10689</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>4119</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>1281</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>10081</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>847</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>847</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>868</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>868</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -3897,32 +3897,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3967,32 +3967,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>889</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -4010,17 +4010,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>182895</t>
+          <t>185210</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>182895</t>
+          <t>185210</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>182895</t>
+          <t>185210</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>88780</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>88780</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>88780</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4080,17 +4080,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>272707</t>
+          <t>273989</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>272707</t>
+          <t>273989</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>272707</t>
+          <t>273989</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4127,32 +4127,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>29747</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17976</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>58086</t>
+          <t>50500</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4162,32 +4162,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>45353</t>
+          <t>49362</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>36678</t>
+          <t>40546</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>56329</t>
+          <t>60422</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>75544</t>
+          <t>79109</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>60934</t>
+          <t>64086</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>96593</t>
+          <t>102355</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -4240,32 +4240,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>83608</t>
+          <t>97873</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>67281</t>
+          <t>79522</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>100294</t>
+          <t>117495</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4275,32 +4275,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>46336</t>
+          <t>52277</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>35704</t>
+          <t>41855</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>56603</t>
+          <t>63827</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4310,32 +4310,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>129944</t>
+          <t>150150</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>112635</t>
+          <t>128407</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>150020</t>
+          <t>171185</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -4353,32 +4353,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>40216</t>
+          <t>49831</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>27512</t>
+          <t>33589</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>56717</t>
+          <t>68059</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4388,32 +4388,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9839</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>29885</t>
+          <t>30168</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4423,32 +4423,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>57671</t>
+          <t>68403</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>42841</t>
+          <t>52155</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>75732</t>
+          <t>88886</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -4466,32 +4466,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>23341</t>
+          <t>24711</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4501,32 +4501,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4536,32 +4536,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>29035</t>
+          <t>32345</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -4579,32 +4579,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4614,32 +4614,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4649,32 +4649,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>9811</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -4692,32 +4692,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>19012</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4727,32 +4727,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4762,32 +4762,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>25652</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>659</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>999</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,27 +5101,27 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>858</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5144,17 +5144,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>176720</t>
+          <t>201855</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>176720</t>
+          <t>201855</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>176720</t>
+          <t>201855</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,17 +5179,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>123619</t>
+          <t>137637</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>123619</t>
+          <t>137637</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>123619</t>
+          <t>137637</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>300339</t>
+          <t>339492</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>300339</t>
+          <t>339492</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>300339</t>
+          <t>339492</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5331,32 +5331,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>11148</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -5374,32 +5374,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>17599</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>12877</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>21387</t>
+          <t>23373</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5409,32 +5409,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5444,32 +5444,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>22056</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>16331</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>27962</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -5487,32 +5487,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>8445</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5522,32 +5522,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>403</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>13624</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -5600,32 +5600,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>478</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5635,32 +5635,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>304</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>440</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>396</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>409</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>409</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -6278,17 +6278,17 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6313,17 +6313,17 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6348,17 +6348,17 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6395,32 +6395,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>19414</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>27465</t>
+          <t>27571</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6430,32 +6430,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>32317</t>
+          <t>32486</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>24765</t>
+          <t>25350</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>40519</t>
+          <t>40919</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6465,32 +6465,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>52098</t>
+          <t>51901</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>42190</t>
+          <t>41139</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>63339</t>
+          <t>62715</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -6508,32 +6508,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>69920</t>
+          <t>69885</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>57379</t>
+          <t>56830</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>81009</t>
+          <t>80291</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6543,32 +6543,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>35522</t>
+          <t>36319</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>28142</t>
+          <t>29145</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>44381</t>
+          <t>45338</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6578,32 +6578,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>105442</t>
+          <t>106204</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>91714</t>
+          <t>93300</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>119757</t>
+          <t>120679</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -6621,32 +6621,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>37027</t>
+          <t>35906</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>25697</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>48461</t>
+          <t>46013</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6656,32 +6656,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>25725</t>
+          <t>25786</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6691,32 +6691,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>54583</t>
+          <t>54296</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>43097</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>68187</t>
+          <t>68452</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -6734,32 +6734,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>19416</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6769,32 +6769,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6804,32 +6804,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -6847,32 +6847,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>20187</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6882,32 +6882,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6917,32 +6917,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>15336</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>9705</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>24784</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -6960,32 +6960,32 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>984</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7030,32 +7030,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>19951</t>
+          <t>17894</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -7073,32 +7073,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7143,17 +7143,17 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -7304,27 +7304,27 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>10466</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -7412,17 +7412,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7447,17 +7447,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7482,17 +7482,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7529,32 +7529,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>71843</t>
+          <t>83587</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>56296</t>
+          <t>66278</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>90164</t>
+          <t>102296</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7564,32 +7564,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>289021</t>
+          <t>95036</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>167123</t>
+          <t>80359</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>364731</t>
+          <t>108346</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7599,32 +7599,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>360864</t>
+          <t>178622</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>212015</t>
+          <t>157904</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>549813</t>
+          <t>206289</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -7642,32 +7642,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>87328</t>
+          <t>100909</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>69816</t>
+          <t>82733</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>104491</t>
+          <t>120492</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7677,32 +7677,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>43989</t>
+          <t>54182</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>14058</t>
+          <t>43672</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>97114</t>
+          <t>67342</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>131317</t>
+          <t>155091</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>53163</t>
+          <t>132956</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>193283</t>
+          <t>176962</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -7755,32 +7755,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>73032</t>
+          <t>81747</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>56474</t>
+          <t>63258</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>95666</t>
+          <t>102121</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7790,32 +7790,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>47199</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>84563</t>
+          <t>58710</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7825,32 +7825,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>111050</t>
+          <t>128946</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>50389</t>
+          <t>107065</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>166209</t>
+          <t>151437</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -7868,32 +7868,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>38688</t>
+          <t>36011</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>24729</t>
+          <t>25137</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>67131</t>
+          <t>49703</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7903,32 +7903,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>17579</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7938,32 +7938,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>50826</t>
+          <t>53590</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>21896</t>
+          <t>40539</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>85866</t>
+          <t>71128</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -7981,32 +7981,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>23362</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>39614</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8016,32 +8016,32 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>16495</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8051,32 +8051,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>21319</t>
+          <t>30664</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>20037</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>36117</t>
+          <t>47030</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -8094,32 +8094,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>11330</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>19573</t>
+          <t>22093</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8164,32 +8164,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>23087</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>33905</t>
+          <t>35868</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -8242,32 +8242,32 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8277,32 +8277,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -8320,32 +8320,32 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8390,32 +8390,32 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>8859</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -8433,32 +8433,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>11191</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8503,32 +8503,32 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>10931</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -8546,17 +8546,17 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>303846</t>
+          <t>346167</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>303846</t>
+          <t>346167</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>303846</t>
+          <t>346167</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8581,17 +8581,17 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>398457</t>
+          <t>233643</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>398457</t>
+          <t>233643</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>398457</t>
+          <t>233643</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8616,17 +8616,17 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>702303</t>
+          <t>579810</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>702303</t>
+          <t>579810</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>702303</t>
+          <t>579810</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8663,32 +8663,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>15060</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>27170</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8698,32 +8698,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8733,32 +8733,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>22111</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>32468</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -8776,32 +8776,32 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>109236</t>
+          <t>125058</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>92617</t>
+          <t>107632</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>124472</t>
+          <t>143507</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8811,32 +8811,32 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>58751</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>43002</t>
+          <t>48948</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>68912</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8846,32 +8846,32 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>161123</t>
+          <t>183809</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>143507</t>
+          <t>161976</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>180765</t>
+          <t>204108</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -8889,102 +8889,102 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>88585</t>
+          <t>101008</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>72661</t>
+          <t>85601</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>103116</t>
+          <t>120406</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
+          <t>27,39%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>38,53%</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>28594</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>21059</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>38189</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>24,87%</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>18,32%</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>33,22%</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>129602</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>112603</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>151026</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>30,32%</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
           <t>26,34%</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>37,38%</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>23670</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>16160</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>31936</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>23,71%</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>16,19%</t>
-        </is>
-      </c>
-      <c r="P76" s="2" t="inlineStr">
-        <is>
-          <t>31,99%</t>
-        </is>
-      </c>
-      <c r="Q76" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="R76" s="2" t="inlineStr">
-        <is>
-          <t>112255</t>
-        </is>
-      </c>
-      <c r="S76" s="2" t="inlineStr">
-        <is>
-          <t>95022</t>
-        </is>
-      </c>
-      <c r="T76" s="2" t="inlineStr">
-        <is>
-          <t>129203</t>
-        </is>
-      </c>
-      <c r="U76" s="2" t="inlineStr">
-        <is>
-          <t>29,88%</t>
-        </is>
-      </c>
-      <c r="V76" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -9002,32 +9002,32 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>20862</t>
+          <t>23004</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>14655</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>30625</t>
+          <t>33466</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9037,32 +9037,32 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9072,32 +9072,32 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>26694</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>34618</t>
+          <t>37412</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -9115,32 +9115,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>21061</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>33480</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9150,32 +9150,32 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>10446</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9185,32 +9185,32 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>26118</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>39320</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -9228,32 +9228,32 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>15740</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>9773</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>27713</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9263,32 +9263,32 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9298,32 +9298,32 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>22234</t>
+          <t>24851</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>15052</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>33021</t>
+          <t>38156</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -9351,12 +9351,12 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9411,22 +9411,22 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>718</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -9464,12 +9464,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -9567,32 +9567,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9602,32 +9602,32 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9637,32 +9637,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -9680,17 +9680,17 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>275865</t>
+          <t>312499</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>275865</t>
+          <t>312499</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>275865</t>
+          <t>312499</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9715,17 +9715,17 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9750,17 +9750,17 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>375689</t>
+          <t>427453</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>375689</t>
+          <t>427453</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>375689</t>
+          <t>427453</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9797,32 +9797,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>345748</t>
+          <t>351699</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>307992</t>
+          <t>316305</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>387547</t>
+          <t>393846</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9832,32 +9832,32 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>548737</t>
+          <t>365973</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>422717</t>
+          <t>336674</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>751416</t>
+          <t>391794</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9867,32 +9867,32 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>894485</t>
+          <t>717672</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>733316</t>
+          <t>671430</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>1398915</t>
+          <t>764239</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -9910,32 +9910,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>637828</t>
+          <t>684819</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>592431</t>
+          <t>637074</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>681719</t>
+          <t>729414</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9945,32 +9945,32 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>262191</t>
+          <t>290144</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>265998</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>336556</t>
+          <t>314606</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9980,32 +9980,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>900019</t>
+          <t>974964</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>657914</t>
+          <t>924903</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>997132</t>
+          <t>1024075</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>39,74%</t>
         </is>
       </c>
     </row>
@@ -10023,32 +10023,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>326676</t>
+          <t>359318</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>293479</t>
+          <t>321521</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>366401</t>
+          <t>397613</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10058,32 +10058,32 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>129762</t>
+          <t>147412</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>75521</t>
+          <t>125658</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>168930</t>
+          <t>169337</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10093,32 +10093,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>456438</t>
+          <t>506730</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>324634</t>
+          <t>462763</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>508338</t>
+          <t>545200</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -10136,32 +10136,32 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>116683</t>
+          <t>115279</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>93262</t>
+          <t>94295</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>153409</t>
+          <t>140892</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10171,32 +10171,32 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>28964</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>25681</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>42022</t>
+          <t>49706</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10206,32 +10206,32 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>145647</t>
+          <t>151728</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>108593</t>
+          <t>126411</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>180258</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -10249,32 +10249,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>61524</t>
+          <t>73362</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>46504</t>
+          <t>56476</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>81747</t>
+          <t>96467</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10284,32 +10284,32 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>25222</t>
+          <t>27966</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>19765</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>38885</t>
+          <t>41932</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10319,32 +10319,32 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>86746</t>
+          <t>101329</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>82515</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>109674</t>
+          <t>126459</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -10362,32 +10362,32 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>51811</t>
+          <t>55075</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>41762</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>68339</t>
+          <t>75899</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10397,32 +10397,32 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>32913</t>
+          <t>39184</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10432,32 +10432,32 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>72673</t>
+          <t>80784</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>53457</t>
+          <t>63230</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>93757</t>
+          <t>103405</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -10475,32 +10475,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10510,32 +10510,32 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10545,32 +10545,32 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -10588,32 +10588,32 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10658,32 +10658,32 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -10701,32 +10701,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10736,32 +10736,32 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10771,32 +10771,32 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>26187</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>33648</t>
+          <t>38236</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -10814,17 +10814,17 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10849,17 +10849,17 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -10884,17 +10884,17 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
